--- a/i_test/test_D6_Table_S1/g_output/D6_Table_S1_attrition_SGLT2i.xlsx
+++ b/i_test/test_D6_Table_S1/g_output/D6_Table_S1_attrition_SGLT2i.xlsx
@@ -477,7 +477,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Soggetti con nessuna dispensazione del farmaco di interesse nei due anni precedenti la data indice</t>
+          <t>Soggetti con nessuna dispensazione del farmaco di interesse precedente alla data indice</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
